--- a/제3자정보제공동의서양식.xlsx
+++ b/제3자정보제공동의서양식.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\com\Desktop\김영진노무사\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\com\Desktop\Project\backup0529\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -20,7 +20,7 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">정보동의서!$A$1:$J$52</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">정보동의서!$A$1:$L$53</definedName>
     <definedName name="범위">'[1]급여대장(출력)'!$C$12:$U$41</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="41">
   <si>
     <t>은(는)</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -260,6 +260,10 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
+    <t xml:space="preserve"> </t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
     <t>{고객사명}</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -270,10 +274,10 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="3">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="179" formatCode="0_);[Red]\(0\)"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="0_);[Red]\(0\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -351,6 +355,23 @@
     </font>
     <font>
       <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0" tint="-0.14999847407452621"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
@@ -498,7 +519,7 @@
     <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="176" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
@@ -533,7 +554,7 @@
     </xf>
     <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -543,7 +564,7 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -574,9 +595,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -620,6 +638,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="22">
@@ -2496,30 +2520,40 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet10"/>
-  <dimension ref="A1:Q52"/>
+  <dimension ref="A1:R52"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="2.625" customWidth="1"/>
-    <col min="2" max="10" width="8.625" customWidth="1"/>
-    <col min="11" max="11" width="1.875" customWidth="1"/>
+    <col min="1" max="1" width="1.875" customWidth="1"/>
+    <col min="2" max="2" width="2.625" customWidth="1"/>
+    <col min="3" max="4" width="8.625" customWidth="1"/>
+    <col min="5" max="5" width="14.75" customWidth="1"/>
+    <col min="6" max="7" width="8.625" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="9" width="10.5" customWidth="1"/>
+    <col min="10" max="10" width="9.25" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="1.625" customWidth="1"/>
+    <col min="13" max="13" width="37.125" customWidth="1"/>
+    <col min="14" max="14" width="34.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="26.25" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="1:18" ht="26.25" x14ac:dyDescent="0.3">
+      <c r="A1" s="5"/>
+      <c r="B1" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="5"/>
-    </row>
-    <row r="2" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="5"/>
+    </row>
+    <row r="2" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="5"/>
       <c r="B2" s="5"/>
       <c r="C2" s="5"/>
@@ -2531,526 +2565,535 @@
       <c r="I2" s="5"/>
       <c r="J2" s="5"/>
       <c r="K2" s="5"/>
-    </row>
-    <row r="3" spans="1:17" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="M3" s="2" t="s">
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:18" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="N3" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3">
+    <row r="4" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4"/>
+      <c r="B4" s="3">
         <v>1</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="C4" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="17"/>
+      <c r="E4" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="E4" s="18" t="s">
+      <c r="F4" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+      <c r="I4" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="J4" s="18"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="4"/>
+      <c r="R4" s="1"/>
+    </row>
+    <row r="5" spans="1:18" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="4"/>
+      <c r="R5" s="1"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="A6" s="4"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18"/>
+      <c r="E6" s="18"/>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
+      <c r="J6" s="18"/>
+      <c r="K6" s="18"/>
+      <c r="L6" s="4"/>
+      <c r="R6" s="1"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C8" s="14" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15"/>
+      <c r="F8" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" s="15"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="J8" s="15"/>
+      <c r="K8" s="16"/>
+    </row>
+    <row r="9" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J9" s="25"/>
+      <c r="K9" s="26"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G10" s="18"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="19"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="22"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C11" s="6" t="s">
+        <v>4</v>
+      </c>
+      <c r="F11" s="19"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="22"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="6"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="22"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="C13" s="20"/>
+      <c r="D13" s="21"/>
+      <c r="E13" s="21"/>
+      <c r="F13" s="10"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="9"/>
+      <c r="I13" s="20"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="27"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="G15" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C17" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16"/>
+      <c r="I17" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="J17" s="15"/>
+      <c r="K17" s="16"/>
+    </row>
+    <row r="18" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J18" s="25"/>
+      <c r="K18" s="26"/>
+    </row>
+    <row r="19" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="F19" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G19" s="18"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="19"/>
+      <c r="J19" s="18"/>
+      <c r="K19" s="22"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C20" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F20" s="19"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="19"/>
+      <c r="J20" s="18"/>
+      <c r="K20" s="22"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G21" s="8"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="20"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="27"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="G23" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="I23" s="13"/>
+      <c r="J23" s="13"/>
+      <c r="K23" s="13"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="Q24" t="s">
         <v>39</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="I4" s="19"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="Q4" s="1"/>
-    </row>
-    <row r="5" spans="1:17" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3"/>
-      <c r="B5" s="19" t="s">
-        <v>32</v>
-      </c>
-      <c r="C5" s="19"/>
-      <c r="D5" s="19"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="4"/>
-      <c r="Q5" s="1"/>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="A6" s="3"/>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="19"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="4"/>
-      <c r="Q6" s="1"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B8" s="15" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15" t="s">
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C25" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="D25" s="15"/>
+      <c r="E25" s="15"/>
+      <c r="F25" s="14" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="16"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="16" t="s">
+      <c r="G25" s="15"/>
+      <c r="H25" s="16"/>
+      <c r="I25" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="I8" s="16"/>
-      <c r="J8" s="17"/>
-    </row>
-    <row r="9" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="6" t="s">
+      <c r="J25" s="15"/>
+      <c r="K25" s="16"/>
+    </row>
+    <row r="26" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C26" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="24" t="s">
+        <v>7</v>
+      </c>
+      <c r="J26" s="25"/>
+      <c r="K26" s="26"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C27" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F27" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="G27" s="18"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="19"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="22"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="C28" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="F28" s="19"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="19"/>
+      <c r="J28" s="18"/>
+      <c r="K28" s="22"/>
+    </row>
+    <row r="29" spans="3:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C29" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D29" s="21"/>
+      <c r="E29" s="27"/>
+      <c r="F29" s="10" t="s">
+        <v>25</v>
+      </c>
+      <c r="G29" s="8"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="20"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="27"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.3">
+      <c r="F31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+    </row>
+    <row r="33" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B33" s="3">
         <v>2</v>
       </c>
-      <c r="E9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G9" s="7"/>
-      <c r="H9" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I9" s="26"/>
-      <c r="J9" s="27"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B10" s="6" t="s">
+      <c r="C33" s="28" t="str">
+        <f>C4</f>
+        <v>{직원명}</v>
+      </c>
+      <c r="D33" s="28"/>
+      <c r="E33" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="F33" s="28" t="str">
+        <f>F4</f>
+        <v>{고객사명}</v>
+      </c>
+      <c r="G33" s="28"/>
+      <c r="H33" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="I33" s="18"/>
+      <c r="J33" s="4"/>
+      <c r="K33" s="4"/>
+    </row>
+    <row r="34" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C34" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="18"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="18"/>
+      <c r="G34" s="18"/>
+      <c r="H34" s="18"/>
+      <c r="I34" s="18"/>
+      <c r="J34" s="18"/>
+      <c r="K34" s="18"/>
+    </row>
+    <row r="35" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C35" s="18"/>
+      <c r="D35" s="18"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="18"/>
+      <c r="G35" s="18"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+      <c r="J35" s="18"/>
+      <c r="K35" s="18"/>
+    </row>
+    <row r="37" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="G37" s="13" t="s">
+        <v>12</v>
+      </c>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+    </row>
+    <row r="39" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B39" s="3">
         <v>3</v>
       </c>
-      <c r="E10" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" s="19"/>
-      <c r="G10" s="23"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="23"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B11" s="6" t="s">
+      <c r="C39" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="D39" s="18"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="18"/>
+      <c r="G39" s="18"/>
+      <c r="H39" s="18"/>
+      <c r="I39" s="18"/>
+      <c r="J39" s="18"/>
+      <c r="K39" s="18"/>
+    </row>
+    <row r="40" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C40" s="18"/>
+      <c r="D40" s="18"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="18"/>
+      <c r="G40" s="18"/>
+      <c r="H40" s="18"/>
+      <c r="I40" s="18"/>
+      <c r="J40" s="18"/>
+      <c r="K40" s="18"/>
+    </row>
+    <row r="41" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="18"/>
+      <c r="G41" s="18"/>
+      <c r="H41" s="18"/>
+      <c r="I41" s="18"/>
+      <c r="J41" s="18"/>
+      <c r="K41" s="18"/>
+    </row>
+    <row r="43" spans="2:11" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B43" s="3">
         <v>4</v>
       </c>
-      <c r="E11" s="20"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="23"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="19"/>
-      <c r="J11" s="23"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B12" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C12" s="19"/>
-      <c r="D12" s="19"/>
-      <c r="E12" s="6"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="20"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="23"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B13" s="21"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="10"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="28"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="F15" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G15" s="14"/>
-      <c r="H15" s="14"/>
-      <c r="I15" s="14"/>
-      <c r="J15" s="14"/>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B17" s="15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F17" s="16"/>
-      <c r="G17" s="17"/>
-      <c r="H17" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I17" s="16"/>
-      <c r="J17" s="17"/>
-    </row>
-    <row r="18" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G18" s="7"/>
-      <c r="H18" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I18" s="26"/>
-      <c r="J18" s="27"/>
-    </row>
-    <row r="19" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="19"/>
-      <c r="G19" s="23"/>
-      <c r="H19" s="20"/>
-      <c r="I19" s="19"/>
-      <c r="J19" s="23"/>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B20" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="E20" s="20"/>
-      <c r="F20" s="19"/>
-      <c r="G20" s="23"/>
-      <c r="H20" s="20"/>
-      <c r="I20" s="19"/>
-      <c r="J20" s="23"/>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B21" s="21"/>
-      <c r="C21" s="22"/>
-      <c r="D21" s="22"/>
-      <c r="E21" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="28"/>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="F23" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="G23" s="14"/>
-      <c r="H23" s="14"/>
-      <c r="I23" s="14"/>
-      <c r="J23" s="14"/>
-    </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B25" s="15" t="s">
-        <v>21</v>
-      </c>
-      <c r="C25" s="16"/>
-      <c r="D25" s="16"/>
-      <c r="E25" s="15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F25" s="16"/>
-      <c r="G25" s="17"/>
-      <c r="H25" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="I25" s="16"/>
-      <c r="J25" s="17"/>
-    </row>
-    <row r="26" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B26" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="G26" s="7"/>
-      <c r="H26" s="25" t="s">
-        <v>7</v>
-      </c>
-      <c r="I26" s="26"/>
-      <c r="J26" s="27"/>
-    </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B27" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="F27" s="19"/>
-      <c r="G27" s="23"/>
-      <c r="H27" s="20"/>
-      <c r="I27" s="19"/>
-      <c r="J27" s="23"/>
-    </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="B28" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E28" s="20"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="23"/>
-      <c r="H28" s="20"/>
-      <c r="I28" s="19"/>
-      <c r="J28" s="23"/>
-    </row>
-    <row r="29" spans="2:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B29" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C29" s="22"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="10" t="s">
-        <v>25</v>
-      </c>
-      <c r="F29" s="8"/>
-      <c r="G29" s="9"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="28"/>
-    </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.3">
-      <c r="E31" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="F31" s="14"/>
-      <c r="G31" s="14"/>
-      <c r="H31" s="14"/>
-      <c r="I31" s="14"/>
-      <c r="J31" s="14"/>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" s="3">
-        <v>2</v>
-      </c>
-      <c r="B33" s="18" t="str">
-        <f>B4</f>
+      <c r="C43" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="D43" s="18"/>
+      <c r="E43" s="18"/>
+      <c r="F43" s="18"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="18"/>
+      <c r="I43" s="18"/>
+      <c r="J43" s="18"/>
+      <c r="K43" s="18"/>
+    </row>
+    <row r="44" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C44" s="18"/>
+      <c r="D44" s="18"/>
+      <c r="E44" s="18"/>
+      <c r="F44" s="18"/>
+      <c r="G44" s="18"/>
+      <c r="H44" s="18"/>
+      <c r="I44" s="18"/>
+      <c r="J44" s="18"/>
+      <c r="K44" s="18"/>
+    </row>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="C45" s="18"/>
+      <c r="D45" s="18"/>
+      <c r="E45" s="18"/>
+      <c r="F45" s="18"/>
+      <c r="G45" s="18"/>
+      <c r="H45" s="18"/>
+      <c r="I45" s="18"/>
+      <c r="J45" s="18"/>
+      <c r="K45" s="18"/>
+    </row>
+    <row r="47" spans="2:11" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="F47" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G47" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="H47" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="48" spans="2:11" s="11" customFormat="1" x14ac:dyDescent="0.3"/>
+    <row r="49" spans="8:11" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H49" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="I49" s="29" t="str">
+        <f>C4</f>
         <v>{직원명}</v>
       </c>
-      <c r="C33" s="18"/>
-      <c r="D33" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="E33" s="18" t="str">
-        <f>E4</f>
+      <c r="J49" s="29"/>
+      <c r="K49" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="8:11" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K50" s="12"/>
+    </row>
+    <row r="51" spans="8:11" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="K51" s="12"/>
+    </row>
+    <row r="52" spans="8:11" s="11" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H52" s="29" t="str">
+        <f>F4</f>
         <v>{고객사명}</v>
       </c>
-      <c r="F33" s="18"/>
-      <c r="G33" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-    </row>
-    <row r="34" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B34" s="19" t="s">
-        <v>29</v>
-      </c>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
-      <c r="G34" s="19"/>
-      <c r="H34" s="19"/>
-      <c r="I34" s="19"/>
-      <c r="J34" s="19"/>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B35" s="19"/>
-      <c r="C35" s="19"/>
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
-      <c r="G35" s="19"/>
-      <c r="H35" s="19"/>
-      <c r="I35" s="19"/>
-      <c r="J35" s="19"/>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="F37" s="14" t="s">
-        <v>12</v>
-      </c>
-      <c r="G37" s="14"/>
-      <c r="H37" s="14"/>
-      <c r="I37" s="14"/>
-      <c r="J37" s="14"/>
-    </row>
-    <row r="39" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="3">
-        <v>3</v>
-      </c>
-      <c r="B39" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="C39" s="19"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
-      <c r="G39" s="19"/>
-      <c r="H39" s="19"/>
-      <c r="I39" s="19"/>
-      <c r="J39" s="19"/>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B40" s="19"/>
-      <c r="C40" s="19"/>
-      <c r="D40" s="19"/>
-      <c r="E40" s="19"/>
-      <c r="F40" s="19"/>
-      <c r="G40" s="19"/>
-      <c r="H40" s="19"/>
-      <c r="I40" s="19"/>
-      <c r="J40" s="19"/>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B41" s="19"/>
-      <c r="C41" s="19"/>
-      <c r="D41" s="19"/>
-      <c r="E41" s="19"/>
-      <c r="F41" s="19"/>
-      <c r="G41" s="19"/>
-      <c r="H41" s="19"/>
-      <c r="I41" s="19"/>
-      <c r="J41" s="19"/>
-    </row>
-    <row r="43" spans="1:10" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="3">
-        <v>4</v>
-      </c>
-      <c r="B43" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="19"/>
-      <c r="D43" s="19"/>
-      <c r="E43" s="19"/>
-      <c r="F43" s="19"/>
-      <c r="G43" s="19"/>
-      <c r="H43" s="19"/>
-      <c r="I43" s="19"/>
-      <c r="J43" s="19"/>
-    </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B44" s="19"/>
-      <c r="C44" s="19"/>
-      <c r="D44" s="19"/>
-      <c r="E44" s="19"/>
-      <c r="F44" s="19"/>
-      <c r="G44" s="19"/>
-      <c r="H44" s="19"/>
-      <c r="I44" s="19"/>
-      <c r="J44" s="19"/>
-    </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="B45" s="19"/>
-      <c r="C45" s="19"/>
-      <c r="D45" s="19"/>
-      <c r="E45" s="19"/>
-      <c r="F45" s="19"/>
-      <c r="G45" s="19"/>
-      <c r="H45" s="19"/>
-      <c r="I45" s="19"/>
-      <c r="J45" s="19"/>
-    </row>
-    <row r="47" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="E47" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="F47" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="G47" s="12" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10" s="11" customFormat="1" x14ac:dyDescent="0.3"/>
-    <row r="49" spans="7:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="G49" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="H49" s="13" t="str">
-        <f>B4</f>
-        <v>{직원명}</v>
-      </c>
-      <c r="I49" s="13"/>
-      <c r="J49" s="12" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="50" spans="7:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="J50" s="12"/>
-    </row>
-    <row r="51" spans="7:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="J51" s="12"/>
-    </row>
-    <row r="52" spans="7:10" s="11" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="G52" s="13" t="str">
-        <f>E4</f>
-        <v>{고객사명}</v>
-      </c>
-      <c r="H52" s="13"/>
-      <c r="I52" s="13"/>
-      <c r="J52" s="12" t="s">
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="12" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="E19:G20"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="F23:J23"/>
-    <mergeCell ref="E31:J31"/>
-    <mergeCell ref="F37:J37"/>
-    <mergeCell ref="H18:J21"/>
-    <mergeCell ref="B25:D25"/>
-    <mergeCell ref="E25:G25"/>
-    <mergeCell ref="H25:J25"/>
-    <mergeCell ref="E27:G28"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="H26:J29"/>
-    <mergeCell ref="B43:J45"/>
-    <mergeCell ref="G52:I52"/>
-    <mergeCell ref="H49:I49"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="G33:H33"/>
-    <mergeCell ref="B34:J35"/>
-    <mergeCell ref="B39:J41"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B5:J6"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="H9:J13"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="E8:G8"/>
-    <mergeCell ref="H8:J8"/>
-    <mergeCell ref="F15:J15"/>
-    <mergeCell ref="B17:D17"/>
-    <mergeCell ref="E17:G17"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="E4:G4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="B12:D13"/>
-    <mergeCell ref="E10:G11"/>
+    <mergeCell ref="F19:H20"/>
+    <mergeCell ref="C21:E21"/>
+    <mergeCell ref="G23:K23"/>
+    <mergeCell ref="F31:K31"/>
+    <mergeCell ref="G37:K37"/>
+    <mergeCell ref="I18:K21"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="F25:H25"/>
+    <mergeCell ref="I25:K25"/>
+    <mergeCell ref="F27:H28"/>
+    <mergeCell ref="C29:E29"/>
+    <mergeCell ref="I26:K29"/>
+    <mergeCell ref="C43:K45"/>
+    <mergeCell ref="H52:J52"/>
+    <mergeCell ref="I49:J49"/>
+    <mergeCell ref="C33:D33"/>
+    <mergeCell ref="F33:G33"/>
+    <mergeCell ref="H33:I33"/>
+    <mergeCell ref="C34:K35"/>
+    <mergeCell ref="C39:K41"/>
+    <mergeCell ref="B1:K1"/>
+    <mergeCell ref="C5:K6"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="I9:K13"/>
+    <mergeCell ref="C8:E8"/>
+    <mergeCell ref="F8:H8"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="G15:K15"/>
+    <mergeCell ref="C17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="F4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="C12:E13"/>
+    <mergeCell ref="F10:H11"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup paperSize="9" scale="80" orientation="portrait" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
 
